--- a/jogos_2025-09-21.xlsx
+++ b/jogos_2025-09-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK265"/>
+  <dimension ref="A1:AK263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45921.23958333334</v>
+        <v>45921.22916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45921.25</v>
+        <v>45921.23958333334</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45921.27083333334</v>
+        <v>45921.25</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45921.29166666666</v>
+        <v>45921.27083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="M61" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>6.5</v>
+        <v>2.62</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45921.35416666666</v>
+        <v>45921.35763888889</v>
       </c>
     </row>
     <row r="66">
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9004,7 +9004,7 @@
         <v>0</v>
       </c>
       <c r="AK66" s="3" t="n">
-        <v>45921.35763888889</v>
+        <v>45921.375</v>
       </c>
     </row>
     <row r="67">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45921.375</v>
+        <v>45921.38541666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45921.38541666666</v>
+        <v>45921.39583333334</v>
       </c>
     </row>
     <row r="77">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N77" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="M79" t="n">
         <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45921.39583333334</v>
+        <v>45921.40625</v>
       </c>
     </row>
     <row r="83">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45921.40625</v>
+        <v>45921.41666666666</v>
       </c>
     </row>
     <row r="85">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N86" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45921.41666666666</v>
+        <v>45921.42708333334</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45921.42708333334</v>
+        <v>45921.4375</v>
       </c>
     </row>
     <row r="101">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45921.4375</v>
+        <v>45921.45138888889</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45921.45138888889</v>
+        <v>45921.45833333334</v>
       </c>
     </row>
     <row r="106">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15162,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15979,27 +15979,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45921.45833333334</v>
+        <v>45921.46875</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45921.45833333334</v>
+        <v>45921.46875</v>
       </c>
     </row>
     <row r="123">
@@ -16237,27 +16237,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16323,10 +16323,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45921.46875</v>
+        <v>45921.47916666666</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45921.46875</v>
+        <v>45921.47916666666</v>
       </c>
     </row>
     <row r="125">
@@ -16495,27 +16495,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45921.47916666666</v>
+        <v>45921.48958333334</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45921.47916666666</v>
+        <v>45921.48958333334</v>
       </c>
     </row>
     <row r="127">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="M127" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N127" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45921.48958333334</v>
+        <v>45921.5</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45921.48958333334</v>
+        <v>45921.5</v>
       </c>
     </row>
     <row r="130">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,16 +17478,16 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,22 +18822,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,22 +19596,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,22 +19854,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20112,22 +20112,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,22 +20628,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21144,22 +21144,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21397,7 +21397,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M163" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N163" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,10 +21477,10 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z163" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -21517,7 +21517,7 @@
         <v>0</v>
       </c>
       <c r="AK163" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.51041666666</v>
       </c>
     </row>
     <row r="164">
@@ -21526,27 +21526,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21646,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.51041666666</v>
       </c>
     </row>
     <row r="165">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="M165" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="N165" t="n">
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,16 +21735,16 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="Z165" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -21775,7 +21775,7 @@
         <v>0</v>
       </c>
       <c r="AK165" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.51041666666</v>
       </c>
     </row>
     <row r="166">
@@ -21784,12 +21784,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21904,7 +21904,7 @@
         <v>0</v>
       </c>
       <c r="AK166" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.51041666666</v>
       </c>
     </row>
     <row r="167">
@@ -21913,27 +21913,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22033,7 +22033,7 @@
         <v>0</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.51736111111</v>
       </c>
     </row>
     <row r="168">
@@ -22042,12 +22042,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22162,7 +22162,7 @@
         <v>0</v>
       </c>
       <c r="AK168" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="169">
@@ -22171,12 +22171,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22291,7 +22291,7 @@
         <v>0</v>
       </c>
       <c r="AK169" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="170">
@@ -22300,12 +22300,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22420,7 +22420,7 @@
         <v>0</v>
       </c>
       <c r="AK170" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="171">
@@ -22429,12 +22429,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22549,7 +22549,7 @@
         <v>0</v>
       </c>
       <c r="AK171" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="172">
@@ -22558,12 +22558,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22678,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="AK172" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="173">
@@ -22687,12 +22687,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,16 +22767,16 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA173" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -22807,7 +22807,7 @@
         <v>0</v>
       </c>
       <c r="AK173" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="174">
@@ -22816,12 +22816,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22936,7 +22936,7 @@
         <v>0</v>
       </c>
       <c r="AK174" s="3" t="n">
-        <v>45921.51041666666</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="175">
@@ -22945,27 +22945,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -23065,7 +23065,7 @@
         <v>0</v>
       </c>
       <c r="AK175" s="3" t="n">
-        <v>45921.51736111111</v>
+        <v>45921.52083333334</v>
       </c>
     </row>
     <row r="176">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23203,12 +23203,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23323,7 +23323,7 @@
         <v>0</v>
       </c>
       <c r="AK177" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.53125</v>
       </c>
     </row>
     <row r="178">
@@ -23332,12 +23332,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23452,7 +23452,7 @@
         <v>0</v>
       </c>
       <c r="AK178" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="179">
@@ -23461,12 +23461,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23581,7 +23581,7 @@
         <v>0</v>
       </c>
       <c r="AK179" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="180">
@@ -23590,27 +23590,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23710,7 +23710,7 @@
         <v>0</v>
       </c>
       <c r="AK180" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="181">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="M181" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="N181" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,16 +23799,16 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="Z181" t="n">
-        <v>2.76</v>
+        <v>1.73</v>
       </c>
       <c r="AA181" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -23839,7 +23839,7 @@
         <v>0</v>
       </c>
       <c r="AK181" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="182">
@@ -23848,12 +23848,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23968,7 +23968,7 @@
         <v>0</v>
       </c>
       <c r="AK182" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="183">
@@ -23977,12 +23977,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24097,7 +24097,7 @@
         <v>0</v>
       </c>
       <c r="AK183" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="184">
@@ -24106,12 +24106,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24147,13 +24147,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24186,10 +24186,10 @@
         <v>0</v>
       </c>
       <c r="Y184" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA184" t="n">
         <v>0</v>
@@ -24226,7 +24226,7 @@
         <v>0</v>
       </c>
       <c r="AK184" s="3" t="n">
-        <v>45921.52083333334</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="185">
@@ -24235,12 +24235,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24355,7 +24355,7 @@
         <v>0</v>
       </c>
       <c r="AK185" s="3" t="n">
-        <v>45921.53125</v>
+        <v>45921.54166666666</v>
       </c>
     </row>
     <row r="186">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25396,12 +25396,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25516,7 +25516,7 @@
         <v>0</v>
       </c>
       <c r="AK194" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.55208333334</v>
       </c>
     </row>
     <row r="195">
@@ -25525,12 +25525,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25645,7 +25645,7 @@
         <v>0</v>
       </c>
       <c r="AK195" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.55208333334</v>
       </c>
     </row>
     <row r="196">
@@ -25654,12 +25654,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25774,7 +25774,7 @@
         <v>0</v>
       </c>
       <c r="AK196" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="197">
@@ -25783,12 +25783,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25903,7 +25903,7 @@
         <v>0</v>
       </c>
       <c r="AK197" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="198">
@@ -25912,12 +25912,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26032,7 +26032,7 @@
         <v>0</v>
       </c>
       <c r="AK198" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="199">
@@ -26041,12 +26041,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26161,7 +26161,7 @@
         <v>0</v>
       </c>
       <c r="AK199" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="200">
@@ -26170,12 +26170,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26290,7 +26290,7 @@
         <v>0</v>
       </c>
       <c r="AK200" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="201">
@@ -26299,12 +26299,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="AK201" s="3" t="n">
-        <v>45921.54166666666</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="202">
@@ -26428,12 +26428,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26548,7 +26548,7 @@
         <v>0</v>
       </c>
       <c r="AK202" s="3" t="n">
-        <v>45921.55208333334</v>
+        <v>45921.5625</v>
       </c>
     </row>
     <row r="203">
@@ -26557,12 +26557,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26677,7 +26677,7 @@
         <v>0</v>
       </c>
       <c r="AK203" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="204">
@@ -26686,12 +26686,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26806,7 +26806,7 @@
         <v>0</v>
       </c>
       <c r="AK204" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="205">
@@ -26815,12 +26815,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26935,7 +26935,7 @@
         <v>0</v>
       </c>
       <c r="AK205" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="206">
@@ -26944,12 +26944,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27064,7 +27064,7 @@
         <v>0</v>
       </c>
       <c r="AK206" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="207">
@@ -27073,12 +27073,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27193,7 +27193,7 @@
         <v>0</v>
       </c>
       <c r="AK207" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="208">
@@ -27202,12 +27202,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27322,7 +27322,7 @@
         <v>0</v>
       </c>
       <c r="AK208" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="209">
@@ -27331,12 +27331,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27451,7 +27451,7 @@
         <v>0</v>
       </c>
       <c r="AK209" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="210">
@@ -27460,12 +27460,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -27540,10 +27540,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z210" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -27580,7 +27580,7 @@
         <v>0</v>
       </c>
       <c r="AK210" s="3" t="n">
-        <v>45921.5625</v>
+        <v>45921.58333333334</v>
       </c>
     </row>
     <row r="211">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27847,12 +27847,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27967,7 +27967,7 @@
         <v>0</v>
       </c>
       <c r="AK213" s="3" t="n">
-        <v>45921.58333333334</v>
+        <v>45921.59375</v>
       </c>
     </row>
     <row r="214">
@@ -27976,12 +27976,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28096,7 +28096,7 @@
         <v>0</v>
       </c>
       <c r="AK214" s="3" t="n">
-        <v>45921.58333333334</v>
+        <v>45921.59375</v>
       </c>
     </row>
     <row r="215">
@@ -28105,27 +28105,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28225,7 +28225,7 @@
         <v>0</v>
       </c>
       <c r="AK215" s="3" t="n">
-        <v>45921.58333333334</v>
+        <v>45921.59375</v>
       </c>
     </row>
     <row r="216">
@@ -28234,12 +28234,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,16 +28314,16 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z216" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>0</v>
       </c>
       <c r="AK216" s="3" t="n">
-        <v>45921.58333333334</v>
+        <v>45921.60416666666</v>
       </c>
     </row>
     <row r="217">
@@ -28363,12 +28363,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28483,7 +28483,7 @@
         <v>0</v>
       </c>
       <c r="AK217" s="3" t="n">
-        <v>45921.58333333334</v>
+        <v>45921.60416666666</v>
       </c>
     </row>
     <row r="218">
@@ -28492,12 +28492,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28612,7 +28612,7 @@
         <v>0</v>
       </c>
       <c r="AK218" s="3" t="n">
-        <v>45921.59375</v>
+        <v>45921.60416666666</v>
       </c>
     </row>
     <row r="219">
@@ -28621,12 +28621,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28741,7 +28741,7 @@
         <v>0</v>
       </c>
       <c r="AK219" s="3" t="n">
-        <v>45921.59375</v>
+        <v>45921.625</v>
       </c>
     </row>
     <row r="220">
@@ -28750,27 +28750,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28870,7 +28870,7 @@
         <v>0</v>
       </c>
       <c r="AK220" s="3" t="n">
-        <v>45921.59375</v>
+        <v>45921.63541666666</v>
       </c>
     </row>
     <row r="221">
@@ -28879,12 +28879,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28999,7 +28999,7 @@
         <v>0</v>
       </c>
       <c r="AK221" s="3" t="n">
-        <v>45921.60416666666</v>
+        <v>45921.64583333334</v>
       </c>
     </row>
     <row r="222">
@@ -29008,12 +29008,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,16 +29088,16 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -29128,7 +29128,7 @@
         <v>0</v>
       </c>
       <c r="AK222" s="3" t="n">
-        <v>45921.60416666666</v>
+        <v>45921.64583333334</v>
       </c>
     </row>
     <row r="223">
@@ -29137,12 +29137,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29257,7 +29257,7 @@
         <v>0</v>
       </c>
       <c r="AK223" s="3" t="n">
-        <v>45921.625</v>
+        <v>45921.64583333334</v>
       </c>
     </row>
     <row r="224">
@@ -29266,12 +29266,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29386,7 +29386,7 @@
         <v>0</v>
       </c>
       <c r="AK224" s="3" t="n">
-        <v>45921.63541666666</v>
+        <v>45921.64583333334</v>
       </c>
     </row>
     <row r="225">
@@ -29395,12 +29395,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
         <v>0</v>
       </c>
       <c r="AK225" s="3" t="n">
-        <v>45921.64583333334</v>
+        <v>45921.65625</v>
       </c>
     </row>
     <row r="226">
@@ -29524,12 +29524,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,16 +29604,16 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -29644,7 +29644,7 @@
         <v>0</v>
       </c>
       <c r="AK226" s="3" t="n">
-        <v>45921.64583333334</v>
+        <v>45921.65625</v>
       </c>
     </row>
     <row r="227">
@@ -29653,27 +29653,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29773,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="AK227" s="3" t="n">
-        <v>45921.64583333334</v>
+        <v>45921.66666666666</v>
       </c>
     </row>
     <row r="228">
@@ -29782,27 +29782,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,16 +29862,16 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -29902,7 +29902,7 @@
         <v>0</v>
       </c>
       <c r="AK228" s="3" t="n">
-        <v>45921.65625</v>
+        <v>45921.66666666666</v>
       </c>
     </row>
     <row r="229">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30943,27 +30943,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31063,7 +31063,7 @@
         <v>0</v>
       </c>
       <c r="AK237" s="3" t="n">
-        <v>45921.66666666666</v>
+        <v>45921.6875</v>
       </c>
     </row>
     <row r="238">
@@ -31072,12 +31072,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31192,7 +31192,7 @@
         <v>0</v>
       </c>
       <c r="AK238" s="3" t="n">
-        <v>45921.66666666666</v>
+        <v>45921.70833333334</v>
       </c>
     </row>
     <row r="239">
@@ -31201,27 +31201,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31321,7 +31321,7 @@
         <v>0</v>
       </c>
       <c r="AK239" s="3" t="n">
-        <v>45921.6875</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="240">
@@ -31330,12 +31330,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31450,7 +31450,7 @@
         <v>0</v>
       </c>
       <c r="AK240" s="3" t="n">
-        <v>45921.70833333334</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="241">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Z247" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32362,12 +32362,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Z248" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32482,7 +32482,7 @@
         <v>0</v>
       </c>
       <c r="AK248" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.75</v>
       </c>
     </row>
     <row r="249">
@@ -32491,27 +32491,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32611,7 +32611,7 @@
         <v>0</v>
       </c>
       <c r="AK249" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.75</v>
       </c>
     </row>
     <row r="250">
@@ -32620,12 +32620,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32740,7 +32740,7 @@
         <v>0</v>
       </c>
       <c r="AK250" s="3" t="n">
-        <v>45921.75</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="251">
@@ -32749,12 +32749,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32869,7 +32869,7 @@
         <v>0</v>
       </c>
       <c r="AK251" s="3" t="n">
-        <v>45921.75</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="252">
@@ -33136,12 +33136,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z254" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33256,7 +33256,7 @@
         <v>0</v>
       </c>
       <c r="AK254" s="3" t="n">
-        <v>45921.79166666666</v>
+        <v>45921.83333333334</v>
       </c>
     </row>
     <row r="255">
@@ -33265,12 +33265,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33385,7 +33385,7 @@
         <v>0</v>
       </c>
       <c r="AK255" s="3" t="n">
-        <v>45921.79166666666</v>
+        <v>45921.83333333334</v>
       </c>
     </row>
     <row r="256">
@@ -33394,12 +33394,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="M256" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N256" t="n">
-        <v>2.55</v>
+        <v>5.6</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,10 +33474,10 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z256" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33514,7 +33514,7 @@
         <v>0</v>
       </c>
       <c r="AK256" s="3" t="n">
-        <v>45921.83333333334</v>
+        <v>45921.85416666666</v>
       </c>
     </row>
     <row r="257">
@@ -33523,12 +33523,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z257" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33643,7 +33643,7 @@
         <v>0</v>
       </c>
       <c r="AK257" s="3" t="n">
-        <v>45921.83333333334</v>
+        <v>45921.85416666666</v>
       </c>
     </row>
     <row r="258">
@@ -33781,12 +33781,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33822,13 +33822,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -33861,10 +33861,10 @@
         <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z259" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AA259" t="n">
         <v>0</v>
@@ -33901,7 +33901,7 @@
         <v>0</v>
       </c>
       <c r="AK259" s="3" t="n">
-        <v>45921.85416666666</v>
+        <v>45921.875</v>
       </c>
     </row>
     <row r="260">
@@ -33910,12 +33910,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,10 +33990,10 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z260" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA260" t="n">
         <v>0</v>
@@ -34030,7 +34030,7 @@
         <v>0</v>
       </c>
       <c r="AK260" s="3" t="n">
-        <v>45921.85416666666</v>
+        <v>45921.89583333334</v>
       </c>
     </row>
     <row r="261">
@@ -34039,12 +34039,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34159,7 +34159,7 @@
         <v>0</v>
       </c>
       <c r="AK261" s="3" t="n">
-        <v>45921.875</v>
+        <v>45921.91666666666</v>
       </c>
     </row>
     <row r="262">
@@ -34168,12 +34168,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34288,7 +34288,7 @@
         <v>0</v>
       </c>
       <c r="AK262" s="3" t="n">
-        <v>45921.89583333334</v>
+        <v>45921.95833333334</v>
       </c>
     </row>
     <row r="263">
@@ -34297,12 +34297,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34417,264 +34417,6 @@
         <v>0</v>
       </c>
       <c r="AK263" s="3" t="n">
-        <v>45921.91666666666</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
-        <v>45921</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Colorado Rapids II</t>
-        </is>
-      </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L264" t="n">
-        <v>0</v>
-      </c>
-      <c r="M264" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" t="n">
-        <v>0</v>
-      </c>
-      <c r="O264" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0</v>
-      </c>
-      <c r="S264" t="n">
-        <v>0</v>
-      </c>
-      <c r="T264" t="n">
-        <v>0</v>
-      </c>
-      <c r="U264" t="n">
-        <v>0</v>
-      </c>
-      <c r="V264" t="n">
-        <v>0</v>
-      </c>
-      <c r="W264" t="n">
-        <v>0</v>
-      </c>
-      <c r="X264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ264" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK264" s="3" t="n">
-        <v>45921.95833333334</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
-        <v>45921</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes II</t>
-        </is>
-      </c>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" t="n">
-        <v>0</v>
-      </c>
-      <c r="I265" t="n">
-        <v>0</v>
-      </c>
-      <c r="J265" t="n">
-        <v>0</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L265" t="n">
-        <v>0</v>
-      </c>
-      <c r="M265" t="n">
-        <v>0</v>
-      </c>
-      <c r="N265" t="n">
-        <v>0</v>
-      </c>
-      <c r="O265" t="n">
-        <v>0</v>
-      </c>
-      <c r="P265" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
-      <c r="R265" t="n">
-        <v>0</v>
-      </c>
-      <c r="S265" t="n">
-        <v>0</v>
-      </c>
-      <c r="T265" t="n">
-        <v>0</v>
-      </c>
-      <c r="U265" t="n">
-        <v>0</v>
-      </c>
-      <c r="V265" t="n">
-        <v>0</v>
-      </c>
-      <c r="W265" t="n">
-        <v>0</v>
-      </c>
-      <c r="X265" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y265" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ265" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK265" s="3" t="n">
         <v>45921.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-21.xlsx
+++ b/jogos_2025-09-21.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK263"/>
+  <dimension ref="A1:AK269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="M74" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="N74" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45921.38541666666</v>
+        <v>45921.375</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45921.39583333334</v>
+        <v>45921.38541666666</v>
       </c>
     </row>
     <row r="77">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M79" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45921.40625</v>
+        <v>45921.39583333334</v>
       </c>
     </row>
     <row r="83">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45921.41666666666</v>
+        <v>45921.40625</v>
       </c>
     </row>
     <row r="85">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45921.42708333334</v>
+        <v>45921.41666666666</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45921.4375</v>
+        <v>45921.42708333334</v>
       </c>
     </row>
     <row r="101">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45921.45138888889</v>
+        <v>45921.4375</v>
       </c>
     </row>
     <row r="105">
@@ -13915,12 +13915,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45921.45833333334</v>
+        <v>45921.45138888889</v>
       </c>
     </row>
     <row r="106">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14904,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15162,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45921.46875</v>
+        <v>45921.45833333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,27 +16108,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45921.46875</v>
+        <v>45921.45833333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,27 +16237,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16323,10 +16323,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45921.47916666666</v>
+        <v>45921.46875</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45921.47916666666</v>
+        <v>45921.46875</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45921.48958333334</v>
+        <v>45921.47916666666</v>
       </c>
     </row>
     <row r="126">
@@ -16624,27 +16624,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="M126" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N126" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,17 +16704,17 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB126" t="n">
         <v>1.65</v>
       </c>
-      <c r="Z126" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
       <c r="AC126" t="n">
         <v>0</v>
       </c>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45921.48958333334</v>
+        <v>45921.47916666666</v>
       </c>
     </row>
     <row r="127">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="M127" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N127" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.48958333334</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45921.5</v>
+        <v>45921.48958333334</v>
       </c>
     </row>
     <row r="130">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,22 +18564,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,22 +19854,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,22 +20112,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,22 +20370,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,22 +21015,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,10 +21477,10 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,22 +22176,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA172" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z214" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,16 +28314,16 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,16 +28443,16 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z217" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,22 +29013,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29395,27 +29395,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
         <v>0</v>
       </c>
       <c r="AK225" s="3" t="n">
-        <v>45921.65625</v>
+        <v>45921.64583333334</v>
       </c>
     </row>
     <row r="226">
@@ -29524,12 +29524,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,16 +29604,16 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
         <v>0</v>
@@ -29644,7 +29644,7 @@
         <v>0</v>
       </c>
       <c r="AK226" s="3" t="n">
-        <v>45921.65625</v>
+        <v>45921.64583333334</v>
       </c>
     </row>
     <row r="227">
@@ -29653,27 +29653,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29733,10 +29733,10 @@
         <v>0</v>
       </c>
       <c r="Y227" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z227" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA227" t="n">
         <v>0</v>
@@ -29773,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="AK227" s="3" t="n">
-        <v>45921.66666666666</v>
+        <v>45921.65625</v>
       </c>
     </row>
     <row r="228">
@@ -29782,27 +29782,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,16 +29862,16 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z228" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA228" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB228" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -29902,7 +29902,7 @@
         <v>0</v>
       </c>
       <c r="AK228" s="3" t="n">
-        <v>45921.66666666666</v>
+        <v>45921.65625</v>
       </c>
     </row>
     <row r="229">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30943,12 +30943,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31063,7 +31063,7 @@
         <v>0</v>
       </c>
       <c r="AK237" s="3" t="n">
-        <v>45921.6875</v>
+        <v>45921.66666666666</v>
       </c>
     </row>
     <row r="238">
@@ -31072,27 +31072,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31192,7 +31192,7 @@
         <v>0</v>
       </c>
       <c r="AK238" s="3" t="n">
-        <v>45921.70833333334</v>
+        <v>45921.66666666666</v>
       </c>
     </row>
     <row r="239">
@@ -31201,27 +31201,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31321,7 +31321,7 @@
         <v>0</v>
       </c>
       <c r="AK239" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.66666666666</v>
       </c>
     </row>
     <row r="240">
@@ -31330,12 +31330,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31450,7 +31450,7 @@
         <v>0</v>
       </c>
       <c r="AK240" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.6875</v>
       </c>
     </row>
     <row r="241">
@@ -31459,27 +31459,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31579,7 +31579,7 @@
         <v>0</v>
       </c>
       <c r="AK241" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.70833333334</v>
       </c>
     </row>
     <row r="242">
@@ -31588,27 +31588,27 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31708,7 +31708,7 @@
         <v>0</v>
       </c>
       <c r="AK242" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.70833333334</v>
       </c>
     </row>
     <row r="243">
@@ -31717,27 +31717,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31837,7 +31837,7 @@
         <v>0</v>
       </c>
       <c r="AK243" s="3" t="n">
-        <v>45921.72916666666</v>
+        <v>45921.70833333334</v>
       </c>
     </row>
     <row r="244">
@@ -31851,22 +31851,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32362,12 +32362,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32482,7 +32482,7 @@
         <v>0</v>
       </c>
       <c r="AK248" s="3" t="n">
-        <v>45921.75</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="249">
@@ -32491,27 +32491,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32611,7 +32611,7 @@
         <v>0</v>
       </c>
       <c r="AK249" s="3" t="n">
-        <v>45921.75</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="250">
@@ -32620,27 +32620,27 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32740,7 +32740,7 @@
         <v>0</v>
       </c>
       <c r="AK250" s="3" t="n">
-        <v>45921.79166666666</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="251">
@@ -32749,27 +32749,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32869,7 +32869,7 @@
         <v>0</v>
       </c>
       <c r="AK251" s="3" t="n">
-        <v>45921.79166666666</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="252">
@@ -32878,27 +32878,27 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32998,7 +32998,7 @@
         <v>0</v>
       </c>
       <c r="AK252" s="3" t="n">
-        <v>45921.79166666666</v>
+        <v>45921.72916666666</v>
       </c>
     </row>
     <row r="253">
@@ -33007,12 +33007,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33127,7 +33127,7 @@
         <v>0</v>
       </c>
       <c r="AK253" s="3" t="n">
-        <v>45921.79166666666</v>
+        <v>45921.75</v>
       </c>
     </row>
     <row r="254">
@@ -33136,12 +33136,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33256,7 +33256,7 @@
         <v>0</v>
       </c>
       <c r="AK254" s="3" t="n">
-        <v>45921.83333333334</v>
+        <v>45921.75</v>
       </c>
     </row>
     <row r="255">
@@ -33265,12 +33265,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33385,7 +33385,7 @@
         <v>0</v>
       </c>
       <c r="AK255" s="3" t="n">
-        <v>45921.83333333334</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="256">
@@ -33394,12 +33394,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,10 +33474,10 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33514,7 +33514,7 @@
         <v>0</v>
       </c>
       <c r="AK256" s="3" t="n">
-        <v>45921.85416666666</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="257">
@@ -33523,12 +33523,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33643,7 +33643,7 @@
         <v>0</v>
       </c>
       <c r="AK257" s="3" t="n">
-        <v>45921.85416666666</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="258">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33772,7 +33772,7 @@
         <v>0</v>
       </c>
       <c r="AK258" s="3" t="n">
-        <v>45921.85416666666</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="259">
@@ -33781,7 +33781,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33901,7 +33901,7 @@
         <v>0</v>
       </c>
       <c r="AK259" s="3" t="n">
-        <v>45921.875</v>
+        <v>45921.79166666666</v>
       </c>
     </row>
     <row r="260">
@@ -33910,12 +33910,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,10 +33990,10 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z260" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA260" t="n">
         <v>0</v>
@@ -34030,7 +34030,7 @@
         <v>0</v>
       </c>
       <c r="AK260" s="3" t="n">
-        <v>45921.89583333334</v>
+        <v>45921.83333333334</v>
       </c>
     </row>
     <row r="261">
@@ -34039,12 +34039,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34159,7 +34159,7 @@
         <v>0</v>
       </c>
       <c r="AK261" s="3" t="n">
-        <v>45921.91666666666</v>
+        <v>45921.83333333334</v>
       </c>
     </row>
     <row r="262">
@@ -34168,12 +34168,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34288,7 +34288,7 @@
         <v>0</v>
       </c>
       <c r="AK262" s="3" t="n">
-        <v>45921.95833333334</v>
+        <v>45921.85416666666</v>
       </c>
     </row>
     <row r="263">
@@ -34297,126 +34297,900 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L263" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M263" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N263" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0</v>
+      </c>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
+        <v>0</v>
+      </c>
+      <c r="U263" t="n">
+        <v>0</v>
+      </c>
+      <c r="V263" t="n">
+        <v>0</v>
+      </c>
+      <c r="W263" t="n">
+        <v>0</v>
+      </c>
+      <c r="X263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK263" s="3" t="n">
+        <v>45921.85416666666</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L264" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M264" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N264" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0</v>
+      </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>0</v>
+      </c>
+      <c r="X264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK264" s="3" t="n">
+        <v>45921.85416666666</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC II</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>0</v>
+      </c>
+      <c r="R265" t="n">
+        <v>0</v>
+      </c>
+      <c r="S265" t="n">
+        <v>0</v>
+      </c>
+      <c r="T265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="n">
+        <v>0</v>
+      </c>
+      <c r="V265" t="n">
+        <v>0</v>
+      </c>
+      <c r="W265" t="n">
+        <v>0</v>
+      </c>
+      <c r="X265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK265" s="3" t="n">
+        <v>45921.875</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Gotham FC</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0</v>
+      </c>
+      <c r="S266" t="n">
+        <v>0</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="n">
+        <v>0</v>
+      </c>
+      <c r="V266" t="n">
+        <v>0</v>
+      </c>
+      <c r="W266" t="n">
+        <v>0</v>
+      </c>
+      <c r="X266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK266" s="3" t="n">
+        <v>45921.89583333334</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M267" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N267" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="n">
+        <v>0</v>
+      </c>
+      <c r="T267" t="n">
+        <v>0</v>
+      </c>
+      <c r="U267" t="n">
+        <v>0</v>
+      </c>
+      <c r="V267" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" t="n">
+        <v>0</v>
+      </c>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK267" s="3" t="n">
+        <v>45921.91666666666</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>LA Galaxy II</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F268" t="inlineStr">
         <is>
           <t>San Jose Earthquakes II</t>
         </is>
       </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" t="n">
-        <v>0</v>
-      </c>
-      <c r="J263" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" t="inlineStr">
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L263" t="n">
-        <v>0</v>
-      </c>
-      <c r="M263" t="n">
-        <v>0</v>
-      </c>
-      <c r="N263" t="n">
-        <v>0</v>
-      </c>
-      <c r="O263" t="n">
-        <v>0</v>
-      </c>
-      <c r="P263" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
-      <c r="R263" t="n">
-        <v>0</v>
-      </c>
-      <c r="S263" t="n">
-        <v>0</v>
-      </c>
-      <c r="T263" t="n">
-        <v>0</v>
-      </c>
-      <c r="U263" t="n">
-        <v>0</v>
-      </c>
-      <c r="V263" t="n">
-        <v>0</v>
-      </c>
-      <c r="W263" t="n">
-        <v>0</v>
-      </c>
-      <c r="X263" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y263" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ263" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK263" s="3" t="n">
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>0</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="n">
+        <v>0</v>
+      </c>
+      <c r="T268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="n">
+        <v>0</v>
+      </c>
+      <c r="V268" t="n">
+        <v>0</v>
+      </c>
+      <c r="W268" t="n">
+        <v>0</v>
+      </c>
+      <c r="X268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK268" s="3" t="n">
+        <v>45921.95833333334</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Colorado Rapids II</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>0</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="n">
+        <v>0</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="n">
+        <v>0</v>
+      </c>
+      <c r="V269" t="n">
+        <v>0</v>
+      </c>
+      <c r="W269" t="n">
+        <v>0</v>
+      </c>
+      <c r="X269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK269" s="3" t="n">
         <v>45921.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-21.xlsx
+++ b/jogos_2025-09-21.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>9.84</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>15.39</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.53</v>
+        <v>1.5</v>
       </c>
       <c r="M67" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>3.04</v>
+        <v>5.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,16 +9093,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9357,10 +9357,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9615,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="M73" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="N73" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10131,10 +10131,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.95</v>
+        <v>2.65</v>
       </c>
       <c r="M93" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="M94" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N94" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14904,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="M127" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N127" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="Z127" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19677,10 +19677,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,22 +19983,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,22 +21015,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,10 +21477,10 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z163" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA172" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,16 +22767,16 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,16 +23154,16 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z179" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z188" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28062,10 +28062,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -28110,22 +28110,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,16 +28443,16 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,16 +28572,16 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -29013,22 +29013,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29271,22 +29271,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,22 +29400,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,22 +29529,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="M227" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="N227" t="n">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29736,13 +29736,13 @@
         <v>1.63</v>
       </c>
       <c r="Z227" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="M228" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="N228" t="n">
-        <v>10.5</v>
+        <v>1.9</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29865,13 +29865,13 @@
         <v>1.63</v>
       </c>
       <c r="Z228" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA228" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB228" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC228" t="n">
         <v>0</v>
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="Z238" t="n">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M244" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N244" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z244" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="M248" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N248" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Z248" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M263" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N263" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Z263" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="M264" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N264" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z264" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G269" t="n">

--- a/jogos_2025-09-21.xlsx
+++ b/jogos_2025-09-21.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="M3" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,14 +1056,14 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.75</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>9.84</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>15.39</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>9.84</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>15.39</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N61" t="n">
         <v>3.15</v>
-      </c>
-      <c r="M61" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.09</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.5</v>
+        <v>2.53</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>3.28</v>
       </c>
       <c r="N67" t="n">
-        <v>5.6</v>
+        <v>3.04</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,16 +9093,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.67</v>
+        <v>2.39</v>
       </c>
       <c r="M69" t="n">
-        <v>4.5</v>
+        <v>3.13</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>2.96</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.53</v>
+        <v>1.5</v>
       </c>
       <c r="M72" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="N72" t="n">
-        <v>3.04</v>
+        <v>5.6</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,16 +9738,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="M73" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N73" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10131,10 +10131,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M80" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,10 +11925,10 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M93" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14904,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16581,10 +16581,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16710,10 +16710,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="M128" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N128" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19677,10 +19677,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -20112,22 +20112,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20193,10 +20193,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23541,10 +23541,10 @@
         <v>0</v>
       </c>
       <c r="Y179" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z179" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA179" t="n">
         <v>0</v>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z187" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z213" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="M214" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N214" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,16 +28056,16 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA214" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -28110,22 +28110,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28191,10 +28191,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,16 +28314,16 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z216" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,16 +28572,16 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,22 +29142,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,22 +29271,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z232" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31113,13 +31113,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z238" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31851,22 +31851,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z244" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z247" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z248" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,10 +32958,10 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA252" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z262" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z264" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>

--- a/jogos_2025-09-21.xlsx
+++ b/jogos_2025-09-21.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.19</v>
+        <v>3.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>9.84</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>15.39</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7035,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="M60" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N60" t="n">
-        <v>2.09</v>
+        <v>2.65</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.53</v>
+        <v>1.67</v>
       </c>
       <c r="M67" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,16 +9093,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9228,10 +9228,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="N69" t="n">
-        <v>2.96</v>
+        <v>1.98</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.5</v>
+        <v>2.39</v>
       </c>
       <c r="M72" t="n">
-        <v>4.7</v>
+        <v>3.13</v>
       </c>
       <c r="N72" t="n">
-        <v>5.6</v>
+        <v>2.96</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,16 +9738,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,10 +11925,10 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N93" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14904,10 +14904,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16065,10 +16065,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16581,10 +16581,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16710,10 +16710,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="M128" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N128" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="M129" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N129" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Homeboyz</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,22 +18564,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,22 +18951,22 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,13 +19632,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -19677,10 +19677,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,22 +19854,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.85</v>
+        <v>1.5</v>
       </c>
       <c r="M153" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="N153" t="n">
-        <v>2.25</v>
+        <v>6.2</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20187,16 +20187,16 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Homeboyz</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,22 +20628,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="M163" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="N163" t="n">
-        <v>2.65</v>
+        <v>8</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,16 +21477,16 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="Z163" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="M165" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="N165" t="n">
-        <v>8</v>
+        <v>2.65</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,16 +21735,16 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AA165" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="M168" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N168" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,16 +22122,16 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Z168" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,16 +23154,16 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24018,13 +24018,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -24057,10 +24057,10 @@
         <v>0</v>
       </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA183" t="n">
         <v>0</v>
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z187" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1.37</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M191" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N191" t="n">
-        <v>7.4</v>
+        <v>1.26</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z192" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z214" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,22 +29013,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,22 +29142,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,22 +29271,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29529,22 +29529,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,22 +30561,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32109,22 +32109,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,10 +32958,10 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
         <v>0</v>
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M262" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="N262" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="Z262" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,10 +34506,10 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z264" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>
